--- a/local/templates/schedule/Schedule.xlsx
+++ b/local/templates/schedule/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Projects/Misc/usaw-owlcms/local/templates/schedule/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Library/Application Support/owlcms/67.4.6/local/templates/schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B27D3806-B271-3744-8F71-C628497CC53F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E93F42-80FD-AC4D-9C0D-BA0B95E1B426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7620" yWindow="2940" windowWidth="33340" windowHeight="20380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1540" yWindow="1960" windowWidth="33020" windowHeight="20380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,17 @@
             <rFont val="Aptos Narrow"/>
             <family val="2"/>
           </rPr>
-          <t>owlcms:fixMerges(4, [1])</t>
+          <t xml:space="preserve">owlcms:mergeDown(4, 1, 1)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+          </rPr>
+          <t>owlcms:verticalBorders(4, 1, 8)</t>
         </r>
       </text>
     </comment>
@@ -229,10 +239,6 @@
     <t>Weight Category</t>
   </si>
   <si>
-    <t># of
-Lifters</t>
-  </si>
-  <si>
     <t>Gender</t>
   </si>
   <si>
@@ -240,6 +246,9 @@
   </si>
   <si>
     <t>${session.name}</t>
+  </si>
+  <si>
+    <t># of</t>
   </si>
 </sst>
 </file>
@@ -720,7 +729,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1">
@@ -737,7 +746,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>13</v>
@@ -746,7 +755,7 @@
         <v>9</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1">
@@ -754,7 +763,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>10</v>
